--- a/Excel Class Files/Part 2 Managing Data with Excel.xlsx
+++ b/Excel Class Files/Part 2 Managing Data with Excel.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Desktop\Excel\Class file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C5F3AF-6734-40C3-8D54-354F6D8D464D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15934D5D-EAA2-4AFD-9EEE-0408FEB942AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
     <sheet name="Managing Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Freeze Pane" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="34">
   <si>
     <t>Country</t>
   </si>
@@ -159,36 +158,17 @@
     <t>5. Learn Hiding/Unhiding Rows and Columns?</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">6. Learn to Freeze and Unfreeze Pan </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="14"/>
-        <color rgb="FF203864"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>( Data in next Sheet)</t>
-    </r>
-  </si>
-  <si>
     <t>7. Learn to Copy, Paste, Paste special and Move data?</t>
   </si>
   <si>
     <t>8. Learn using format painter to copy format?</t>
-  </si>
-  <si>
-    <t>9. Learn Renaming worksheets?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,14 +188,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -245,16 +217,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="14"/>
-      <color rgb="FF203864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,18 +245,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -553,42 +511,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="8"/>
-      </right>
-      <top style="thin">
-        <color theme="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -615,14 +542,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1888,1091 +1812,549 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E085692E-98F8-453D-92F3-5F59A7B7E3A8}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="4.28515625" customWidth="1"/>
     <col min="10" max="10" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="30" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:10" s="27" customFormat="1" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+    <row r="3" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:10" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="30" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>35</v>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>450</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>3150</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>1200</v>
+      </c>
+      <c r="I13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>425</v>
+      </c>
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14">
+        <v>850</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>450</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>500</v>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" t="s">
-        <v>6</v>
-      </c>
-      <c r="J14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>450</v>
-      </c>
-      <c r="E15">
-        <v>7</v>
-      </c>
       <c r="F15">
-        <v>3150</v>
+        <v>1500</v>
       </c>
       <c r="G15" t="s">
         <v>9</v>
       </c>
       <c r="H15">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>850</v>
+        <v>1400</v>
       </c>
       <c r="G16" t="s">
         <v>9</v>
       </c>
       <c r="H16">
-        <v>450</v>
+        <v>-100</v>
       </c>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>350</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>1750</v>
+      </c>
+      <c r="G17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17">
+        <v>700</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17">
-        <v>500</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>1500</v>
-      </c>
-      <c r="G17" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17">
-        <v>300</v>
-      </c>
-      <c r="I17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D18">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="E18">
         <v>4</v>
       </c>
       <c r="F18">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H18">
-        <v>-100</v>
+        <v>450</v>
       </c>
       <c r="I18" t="s">
         <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1750</v>
+        <v>1500</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H19">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D20">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H20">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>450</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D22">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>300</v>
+        <v>-250</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>300</v>
+        <v>2800</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H23">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24">
         <v>600</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="H24">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D25">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>2800</v>
+        <v>1350</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="I25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G26" t="s">
         <v>23</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D27">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>1350</v>
+        <v>4900</v>
       </c>
       <c r="G27" t="s">
         <v>23</v>
       </c>
       <c r="H27">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D28">
-        <v>300</v>
+        <v>650</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H28">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="I28" t="s">
         <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D29">
         <v>700</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29">
-        <v>4900</v>
+        <v>3500</v>
       </c>
       <c r="G29" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H29">
-        <v>550</v>
+        <v>-100</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F30">
-        <v>2600</v>
+        <v>3150</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="I30" t="s">
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31">
-        <v>700</v>
-      </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
-      <c r="F31">
-        <v>3500</v>
-      </c>
-      <c r="G31" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31">
-        <v>-100</v>
-      </c>
-      <c r="I31" t="s">
-        <v>10</v>
-      </c>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32">
-        <v>450</v>
-      </c>
-      <c r="E32">
-        <v>7</v>
-      </c>
-      <c r="F32">
-        <v>3150</v>
-      </c>
-      <c r="G32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>1200</v>
-      </c>
-      <c r="I32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D8EA90-6AB8-4FD7-85CD-A5E6FCE2728A}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>450</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D19" si="0">B2*C2</f>
-        <v>3150</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>1200</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>425</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>450</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>500</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>300</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>350</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>1400</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>-100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>350</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>1750</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>700</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>450</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7">
-        <v>450</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>500</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>250</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>300</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>300</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>450</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <v>600</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11">
-        <v>-250</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <v>700</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>2800</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>350</v>
-      </c>
-      <c r="G12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>600</v>
-      </c>
-      <c r="C13">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>450</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>1350</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14">
-        <v>500</v>
-      </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15">
-        <v>300</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15">
-        <v>350</v>
-      </c>
-      <c r="G15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>700</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>4900</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16">
-        <v>550</v>
-      </c>
-      <c r="G16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17">
-        <v>650</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>2600</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17">
-        <v>400</v>
-      </c>
-      <c r="G17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>700</v>
-      </c>
-      <c r="C18">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>3500</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>-100</v>
-      </c>
-      <c r="G18" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19">
-        <v>450</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>3150</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19">
-        <v>1200</v>
-      </c>
-      <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s">
         <v>15</v>
       </c>
     </row>
